--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,142 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130010895</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57753</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Branten i granskogen, Röra Strand, Tjörn, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>303024</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6438891</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sökte föda i äldre granar.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sverker Molander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sverker Molander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,264 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130050653</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97669</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nära våtmarken Furusäter, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>302905</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6438528</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130052560</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nära våtmarken Furusäter, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>302905</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6438528</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hackad död tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linéa Björnsdotter</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -944,7 +944,7 @@
         <v>130050653</v>
       </c>
       <c r="B4" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -944,7 +944,7 @@
         <v>130050653</v>
       </c>
       <c r="B4" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97452</v>
+        <v>97454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -808,7 +808,7 @@
         <v>130010895</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>130050653</v>
       </c>
       <c r="B4" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>130052560</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>130148146</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>97541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>130148279</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>130148288</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97541</v>
+        <v>97544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1202,7 +1202,7 @@
         <v>130148146</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97544</v>
+        <v>97570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>130148279</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>130148288</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97570</v>
+        <v>97571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97571</v>
+        <v>97572</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97572</v>
+        <v>97648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,6 +1340,10 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stigfjordens naturreservat, Stigfjordens naturreservat, Boh</t>
@@ -1398,8 +1402,9 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97648</v>
+        <v>97649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97649</v>
+        <v>97650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
+        <v>97653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97653</v>
+        <v>97659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97659</v>
+        <v>97662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97662</v>
+        <v>97667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97667</v>
+        <v>97669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -1314,7 +1314,7 @@
         <v>130148333</v>
       </c>
       <c r="B7" t="n">
-        <v>97710</v>
+        <v>97713</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56290-2025 artfynd.xlsx
+++ b/artfynd/A 56290-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104376229</v>
+        <v>130148333</v>
       </c>
       <c r="B2" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Furusäter, NV 550m , Boh</t>
+          <t>Stigfjordens naturreservat, Stigfjordens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>303041.4664548521</v>
+        <v>303042</v>
       </c>
       <c r="R2" t="n">
-        <v>6438480.482237468</v>
+        <v>6438713</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>de flesta små plantor</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lasse Johnson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lasse Johnson</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130010895</v>
+        <v>132798819</v>
       </c>
       <c r="B3" t="n">
-        <v>57839</v>
+        <v>79992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,61 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Branten i granskogen, Röra Strand, Tjörn, Boh</t>
+          <t>Nära våtmarken Furusäter, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>303024</v>
+        <v>302905</v>
       </c>
       <c r="R3" t="n">
-        <v>6438891</v>
+        <v>6438528</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -894,27 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sökte föda i äldre granar.</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,50 +876,60 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>stereolupp</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sverker Molander</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sverker Molander</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130050653</v>
+        <v>130010895</v>
       </c>
       <c r="B4" t="n">
-        <v>97791</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -974,14 +937,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -991,17 +959,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nära våtmarken Furusäter, Boh</t>
+          <t>Branten i granskogen, Röra Strand, Tjörn, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>302905</v>
+        <v>303024</v>
       </c>
       <c r="R4" t="n">
-        <v>6438528</v>
+        <v>6438891</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1025,22 +993,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sökte föda i äldre granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,31 +1024,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Sverker Molander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Sverker Molander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130052560</v>
+        <v>130150631</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1100,30 +1068,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nära våtmarken Furusäter, Boh</t>
+          <t>Stigfjordens naturreservat, Stigfjordens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>302905</v>
+        <v>302937</v>
       </c>
       <c r="R5" t="n">
-        <v>6438528</v>
+        <v>6438904</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,27 +1114,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hackad död tall</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,35 +1140,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linéa Björnsdotter</t>
+          <t>Suzi B Jagre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130148146</v>
+        <v>130052560</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1228,16 +1185,26 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stigfjordens naturreservat, Stigfjordens naturreservat, Boh</t>
+          <t>Nära våtmarken Furusäter, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>303030</v>
+        <v>302905</v>
       </c>
       <c r="R6" t="n">
-        <v>6438466</v>
+        <v>6438528</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1264,27 +1231,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hackspår i stående död tall</t>
+          <t>Hackad död tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,26 +1262,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Suzi B Jagre</t>
+          <t>Linéa Björnsdotter</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130148333</v>
+        <v>130148146</v>
       </c>
       <c r="B7" t="n">
-        <v>97713</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,38 +1294,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stigfjordens naturreservat, Stigfjordens naturreservat, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>303042</v>
+        <v>303030</v>
       </c>
       <c r="R7" t="n">
-        <v>6438713</v>
+        <v>6438466</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1385,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1395,7 +1363,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hackspår i stående död tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,7 +1377,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,11 +1398,11 @@
         <v>130148279</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1538,11 +1510,11 @@
         <v>130148288</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1650,11 +1622,11 @@
         <v>132794628</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1769,48 +1741,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132798819</v>
+        <v>104376229</v>
       </c>
       <c r="B11" t="n">
-        <v>79952</v>
+        <v>98194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220686</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nära våtmarken Furusäter, Boh</t>
+          <t>Furusäter, NV 550m , Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>302905</v>
+        <v>303041</v>
       </c>
       <c r="R11" t="n">
-        <v>6438528</v>
+        <v>6438480</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1834,22 +1818,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2022-10-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>de flesta små plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1858,31 +1837,153 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>stereolupp</t>
-        </is>
-      </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Lasse Johnson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lasse Johnson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130050653</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nära våtmarken Furusäter, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>302905</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6438528</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tjörn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stenkyrka</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Linéa Björnsdotter</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Linéa Björnsdotter</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
